--- a/doanmon/FILE_LOI_2_GIA_TRI_KHONG_HOP_LE.xlsx
+++ b/doanmon/FILE_LOI_2_GIA_TRI_KHONG_HOP_LE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>productCode</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Price is Zero</t>
   </si>
   <si>
-    <t>Chocolate</t>
+    <t>Birthday Cakes</t>
   </si>
   <si>
     <t>price must be &gt; 0</t>
@@ -50,7 +50,7 @@
     <t>Negative Price</t>
   </si>
   <si>
-    <t>Vanilla</t>
+    <t>Wedding Cakes</t>
   </si>
   <si>
     <t>price is negative</t>
@@ -62,7 +62,7 @@
     <t>Price Too High</t>
   </si>
   <si>
-    <t>Fruit</t>
+    <t>Cheese Cakes</t>
   </si>
   <si>
     <t>price exceeds 1000000</t>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Quantity is Decimal</t>
+  </si>
+  <si>
+    <t>Gataux</t>
   </si>
   <si>
     <t>quantity must be integer</t>
@@ -279,93 +282,93 @@
         <v>25.99</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>10.5</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>18.5</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>-5.0</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>22.5</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>200000.0</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>25.99</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
